--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="292">
   <si>
     <t/>
   </si>
@@ -872,6 +872,21 @@
   </si>
   <si>
     <t>G/F FRS MLK F/CRM320</t>
+  </si>
+  <si>
+    <t>20144001</t>
+  </si>
+  <si>
+    <t>B.F RYL B/GRG MRCN55</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>20144002</t>
+  </si>
+  <si>
+    <t>B.F RYL B/GRG KEJU55</t>
   </si>
 </sst>
 </file>
@@ -1264,13 +1279,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3854,6 +3870,46 @@
         <v>226</v>
       </c>
     </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="294">
   <si>
     <t/>
   </si>
@@ -887,6 +887,12 @@
   </si>
   <si>
     <t>B.F RYL B/GRG KEJU55</t>
+  </si>
+  <si>
+    <t>20144000</t>
+  </si>
+  <si>
+    <t>FSTA SS AYM S/GPRK60</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3910,6 +3916,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
